--- a/public/post/drafts/season-prediction/men_simple-model-tests-predicted_mae.xlsx
+++ b/public/post/drafts/season-prediction/men_simple-model-tests-predicted_mae.xlsx
@@ -636,25 +636,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>0.149123748477365</v>
+        <v>0.153860604773535</v>
       </c>
       <c r="C10" t="n">
-        <v>0.118230039290075</v>
+        <v>0.119937169347045</v>
       </c>
       <c r="D10" t="n">
-        <v>0.122426116525778</v>
+        <v>0.129674847957529</v>
       </c>
       <c r="E10" t="n">
-        <v>0.126061676922966</v>
+        <v>0.138291833788249</v>
       </c>
       <c r="F10" t="n">
-        <v>0.113210447867902</v>
+        <v>0.114797199976344</v>
       </c>
       <c r="G10" t="n">
-        <v>0.132273788508601</v>
+        <v>0.133748186252438</v>
       </c>
       <c r="H10" t="n">
-        <v>0.126887636265448</v>
+        <v>0.131718307015857</v>
       </c>
     </row>
     <row r="11">
